--- a/miranda_sales_analysis.results.Q5.xlsx
+++ b/miranda_sales_analysis.results.Q5.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{379DD954-C6B4-4E72-8570-5B4C157B59AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DB6E85-3F47-43ED-9801-E16CB0411DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80E70CF5-6910-4C5F-A1A5-6B127F102DCA}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -558,9 +558,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -735,20 +734,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -805,20 +791,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -875,18 +848,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -943,18 +905,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1011,20 +962,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1081,20 +1019,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1151,24 +1076,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1225,20 +1133,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2378,12 +2273,42 @@
           </c:spPr>
         </c:majorGridlines>
         <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>STORE</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> LOCATION</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
           <c:layout>
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.43093860199990347"/>
-              <c:y val="0.82877515310586192"/>
+              <c:x val="0.43093859166320325"/>
+              <c:y val="0.91128349055377977"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3277,7 +3202,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{89056281-AD90-4396-A3D6-930ABF7796D1}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{89056281-AD90-4396-A3D6-930ABF7796D1}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A1:J11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisCol" showAll="0">
@@ -3828,15 +3753,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B2">
@@ -3868,178 +3793,122 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>322100.07</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1">
+      <c r="J3">
         <v>322100.07</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>283455.62</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1">
+      <c r="J4">
         <v>283455.62</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>309592.06</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1">
+      <c r="J5">
         <v>309592.06</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>286217.15000000002</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1">
+      <c r="J6">
         <v>286217.15000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>286779.43</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1">
+      <c r="J7">
         <v>286779.43</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>331116.76</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1">
+      <c r="J8">
         <v>331116.76</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>277310.18</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>277310.18</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>295651.17</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>295651.17</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>322100.07</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>283455.62</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>309592.06</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>286217.15000000002</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>286779.43</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>331116.76</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>277310.18</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11">
         <v>295651.17</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11">
         <v>2392222.44</v>
       </c>
     </row>
